--- a/MADE-2.0/matlab/CS/input/WP_CS_input_template.xlsx
+++ b/MADE-2.0/matlab/CS/input/WP_CS_input_template.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1283,25 +1283,25 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Materials &amp; allowables</t>
+          <t>Geometric consistency checks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>F_z_check_MN</t>
+          <t>SC_w_min</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>35</v>
+        <v>0.005</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Axial force used in the final stress check. OPEN QUESTION: the legacy driver (CS_opt_VNS.m) computed FZmax from EMAG_FIELD_FORCES and then immediately overwrote it with this fixed value - carried over unchanged, see manuale CS 'decisioni aperte'.</t>
+          <t>Minimum admissible SC cable width</t>
         </is>
       </c>
     </row>
@@ -1313,20 +1313,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SC_w_min</t>
+          <t>r_cable_min</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.005</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Minimum admissible SC cable width</t>
+          <t>Minimum admissible cable aspect ratio Cond_h/Cond_w</t>
         </is>
       </c>
     </row>
@@ -1338,11 +1338,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>r_cable_min</t>
+          <t>r_cable_max</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Minimum admissible cable aspect ratio Cond_h/Cond_w</t>
+          <t>Maximum admissible cable aspect ratio Cond_h/Cond_w</t>
         </is>
       </c>
     </row>
@@ -1363,20 +1363,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>r_cable_max</t>
+          <t>JT_min_check</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2.5</v>
+        <v>0.001</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maximum admissible cable aspect ratio Cond_h/Cond_w</t>
+          <t>Minimum admissible jacket thickness (post-sizing check)</t>
         </is>
       </c>
     </row>
@@ -1388,11 +1388,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JT_min_check</t>
+          <t>Ri_min</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.001</v>
+        <v>0.3</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1400,31 +1400,6 @@
         </is>
       </c>
       <c r="E39" t="inlineStr">
-        <is>
-          <t>Minimum admissible jacket thickness (post-sizing check)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Geometric consistency checks</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Ri_min</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
         <is>
           <t>Minimum admissible winding-pack inner radius</t>
         </is>
@@ -1508,7 +1483,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>This is a direct port of CS_opt_VNS.m (2026-09-29). See the 'Manuale CS' artifact for the full legacy-file</t>
+          <t>This is a direct port of CS_opt_VNS.m (2026-09-29, updated 2026-10-01). See the 'Manuale CS' artifact for the full legacy-file</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1497,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>(notably F_z_check_MN and the Ic_sst33 argument order, see the corresponding cell/function comments).</t>
+          <t>(notably the Ic_sst33 argument order in the HTS branch, see the corresponding function comment).</t>
         </is>
       </c>
     </row>

--- a/MADE-2.0/matlab/CS/input/WP_CS_input_template.xlsx
+++ b/MADE-2.0/matlab/CS/input/WP_CS_input_template.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1402,6 +1402,256 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>Minimum admissible winding-pack inner radius</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fem_mesh_r</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Elements per conductor cell, radial</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fem_mesh_z</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Elements per conductor cell, axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fem_subfil</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>n x n current sub-filaments per turn (self field)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fem_bg_fil_r</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Radial filaments per background coil block (PF, plasma)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fem_bg_fil_z</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Axial filaments per background coil block (PF, plasma)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fem_bc</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Stack support: 1 inertia relief, 2 bottom face fixed axially</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fem_nu_wp</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Poisson ratio of the homogenized winding pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fem_nu_ins</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Poisson ratio of the ground insulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fem_nu_steel</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Poisson ratio of the spacer plates</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fem_preload_MN</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Stack preload on the top face (needs fem_bc = 2)</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1679,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1479,7 +1728,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>

--- a/MADE-2.0/matlab/CS/input/WP_CS_input_template.xlsx
+++ b/MADE-2.0/matlab/CS/input/WP_CS_input_template.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1652,6 +1652,106 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>Stack preload on the top face (needs fem_bc = 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fem_detail_module</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Module (1..n_moduli) modeled turn by turn in the FEM, 0 = all homogenized</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>fem_detail_cable_r</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Elements across the cable of a turn, radial (detailed module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>fem_detail_cable_z</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Elements across the cable of a turn, axial (detailed module)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>FEM verification</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>fem_nu_cable</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Poisson ratio of the cable in the detailed module</t>
         </is>
       </c>
     </row>
